--- a/Result/profitability/3552.xlsx
+++ b/Result/profitability/3552.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.22625</v>
+        <v>0.00874999999999998</v>
       </c>
       <c r="N2" t="n">
-        <v>21.00375</v>
+        <v>19.9225</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -693,7 +693,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>97.09999999999999</v>
@@ -780,10 +780,10 @@
         <v>1.37</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3725000000000001</v>
+        <v>0.15125</v>
       </c>
       <c r="N3" t="n">
-        <v>22.16375</v>
+        <v>21.1</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>97.2</v>
@@ -899,10 +899,10 @@
         <v>0.47</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4025</v>
+        <v>0.19875</v>
       </c>
       <c r="N4" t="n">
-        <v>23.4</v>
+        <v>22.40625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>97.3</v>
@@ -1018,10 +1018,10 @@
         <v>0.09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4025</v>
+        <v>0.19875</v>
       </c>
       <c r="N5" t="n">
-        <v>24.59125</v>
+        <v>23.7425</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,13 +1137,13 @@
         <v>0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0.43625</v>
+        <v>0.2175</v>
       </c>
       <c r="N6" t="n">
-        <v>25.4475</v>
+        <v>24.585</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,13 +1155,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,10 +1264,10 @@
         <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>0.56375</v>
+        <v>0.335</v>
       </c>
       <c r="N7" t="n">
-        <v>26.8475</v>
+        <v>25.8325</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>1.79</v>
       </c>
       <c r="M8" t="n">
-        <v>0.75125</v>
+        <v>0.5575</v>
       </c>
       <c r="N8" t="n">
-        <v>28.465</v>
+        <v>27.58</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3552</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2156</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1912</v>
+      </c>
+      <c r="E75" t="n">
+        <v>245</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-165</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-7.66%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-154</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-151</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.05250000000000002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-155</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-7.08</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3841562669560499</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-18.11111111111111</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-6.790000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3743109151047409</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
